--- a/주력상품_테스트_예시.xlsx
+++ b/주력상품_테스트_예시.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IRENE_XD\Documents\카카오톡 받은 파일\buyma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9884C31E-45EB-4297-A2B7-9938DFB16D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD4EAFA-4FCF-4625-A3A0-653A92A56C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{07B43B4F-2B15-4CC6-9A51-92B0E28D71C5}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15345" xr2:uid="{07B43B4F-2B15-4CC6-9A51-92B0E28D71C5}"/>
   </bookViews>
   <sheets>
     <sheet name="주력상품_테스트_예시" sheetId="1" r:id="rId1"/>
@@ -20,37 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>Nike Air Jordan 1 High OG Chicago</t>
-  </si>
-  <si>
-    <t>Adidas Yeezy Boost 350 V2 Zebra</t>
-  </si>
-  <si>
-    <t>Louis Vuitton Neverfull MM Monogram</t>
-  </si>
-  <si>
-    <t>Chanel Classic Flap Bag Medium</t>
-  </si>
-  <si>
-    <t>Herm챔s Birkin 30 Togo Leather</t>
-  </si>
-  <si>
-    <t>Gucci GG Marmont Small Shoulder Bag</t>
-  </si>
-  <si>
-    <t>Prada Re-Edition 2005 Nylon Bag</t>
-  </si>
-  <si>
-    <t>Bottega Veneta Intrecciato Cassette Bag</t>
-  </si>
-  <si>
-    <t>Dior Lady Dior Medium Bag</t>
-  </si>
-  <si>
-    <t>Balenciaga City Classic Bag</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>상품명</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -58,6 +28,15 @@
   <si>
     <t>상품ID</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BURBERRY Monogram Ball cap</t>
+  </si>
+  <si>
+    <t>402562-01</t>
+  </si>
+  <si>
+    <t>STUSSY Globe Varsity Jacket Black</t>
   </si>
 </sst>
 </file>
@@ -1029,95 +1008,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2E1A052-4655-4B83-A1E1-5BFBA7E8891E}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2">
-        <v>12345678</v>
+        <v>120769951</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>87654321</v>
+        <v>122705188</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B4">
-        <v>11223344</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>55667788</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>99887766</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>44556677</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>33445566</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9">
-        <v>22334455</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>66778899</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>77889900</v>
+        <v>121649725</v>
       </c>
     </row>
   </sheetData>
